--- a/doc/Propuesta_cursoRbase.xlsx
+++ b/doc/Propuesta_cursoRbase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unitednations-my.sharepoint.com/personal/andres_gutierrez_un_org/Documents/CEPAL/Vademecum/1. Moodle/Ciencia de datos con R/admin/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\DAT\SAECEPAL\Recursos\Entrenamiento\2025_CursoRbase\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="150" documentId="8_{007230C6-3620-4F4C-8810-862E34ECBBAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF9649BC-CB5B-C64D-9E67-31364FB19188}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F78BCBD-3A3C-4A33-BECC-BFFC0AFEC7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{E0571C12-E740-4320-B6A4-84CBC13E1707}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E0571C12-E740-4320-B6A4-84CBC13E1707}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -284,12 +284,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -330,7 +336,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -338,16 +344,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -685,16 +697,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A52B075E-DA0A-4FC8-90FD-7548AB994679}">
   <dimension ref="A1:D51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="2"/>
-    <col min="4" max="4" width="60.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="2"/>
+    <col min="1" max="1" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
+    <col min="4" max="4" width="60.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>61</v>
       </c>
@@ -708,281 +720,281 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="6">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="1">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="6">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="1">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="6">
         <v>3</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="1">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="6">
         <v>4</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="1">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="6">
         <v>5</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="6">
         <v>1</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="1">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="6">
         <v>2</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="1">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="6">
         <v>3</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="1">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="6">
         <v>4</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="1">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="6">
         <v>5</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="6">
         <v>1</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="1">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="6">
         <v>2</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="1">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="6">
         <v>3</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="1">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="6">
         <v>4</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="1">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="6">
         <v>5</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="6">
         <v>1</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="1">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="6">
         <v>2</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="1">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="6">
         <v>3</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="1">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="6">
         <v>4</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="1">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="6">
         <v>5</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="6">
         <v>1</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="1">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="6">
         <v>2</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="1">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="6">
         <v>3</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="1">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="6">
         <v>4</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="1">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="6">
         <v>5</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C27" s="1">
@@ -992,9 +1004,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
       <c r="C28" s="1">
         <v>2</v>
       </c>
@@ -1002,9 +1014,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
       <c r="C29" s="1">
         <v>3</v>
       </c>
@@ -1012,9 +1024,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
       <c r="C30" s="1">
         <v>4</v>
       </c>
@@ -1022,9 +1034,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
       <c r="C31" s="1">
         <v>5</v>
       </c>
@@ -1032,11 +1044,11 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C32" s="1">
@@ -1046,9 +1058,9 @@
         <v>53</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
       <c r="C33" s="1">
         <v>2</v>
       </c>
@@ -1056,9 +1068,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
       <c r="C34" s="1">
         <v>3</v>
       </c>
@@ -1066,9 +1078,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
       <c r="C35" s="1">
         <v>4</v>
       </c>
@@ -1076,21 +1088,21 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
       <c r="C36" s="1">
         <v>5</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D36" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="3" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C37" s="1">
@@ -1100,9 +1112,9 @@
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
       <c r="C38" s="1">
         <v>2</v>
       </c>
@@ -1110,9 +1122,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
       <c r="C39" s="1">
         <v>3</v>
       </c>
@@ -1120,9 +1132,9 @@
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
       <c r="C40" s="1">
         <v>4</v>
       </c>
@@ -1130,9 +1142,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
       <c r="C41" s="1">
         <v>5</v>
       </c>
@@ -1140,11 +1152,11 @@
         <v>51</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C42" s="1">
@@ -1154,9 +1166,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
       <c r="C43" s="1">
         <v>2</v>
       </c>
@@ -1164,9 +1176,9 @@
         <v>47</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="4"/>
+      <c r="B44" s="4"/>
       <c r="C44" s="1">
         <v>3</v>
       </c>
@@ -1174,9 +1186,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
       <c r="C45" s="1">
         <v>4</v>
       </c>
@@ -1184,9 +1196,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
       <c r="C46" s="1">
         <v>5</v>
       </c>
@@ -1194,11 +1206,11 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="4" t="s">
         <v>72</v>
       </c>
       <c r="C47" s="1">
@@ -1208,9 +1220,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="4"/>
+      <c r="B48" s="4"/>
       <c r="C48" s="1">
         <v>2</v>
       </c>
@@ -1218,9 +1230,9 @@
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="4"/>
+      <c r="B49" s="4"/>
       <c r="C49" s="1">
         <v>3</v>
       </c>
@@ -1228,9 +1240,9 @@
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="3"/>
-      <c r="B50" s="3"/>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
       <c r="C50" s="1">
         <v>4</v>
       </c>
@@ -1238,9 +1250,9 @@
         <v>59</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="4"/>
+      <c r="B51" s="4"/>
       <c r="C51" s="1">
         <v>5</v>
       </c>
@@ -1250,6 +1262,10 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="A27:A31"/>
     <mergeCell ref="A47:A51"/>
     <mergeCell ref="A37:A41"/>
     <mergeCell ref="B2:B6"/>
@@ -1266,10 +1282,6 @@
     <mergeCell ref="A42:A46"/>
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="A7:A11"/>
-    <mergeCell ref="A12:A16"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A26"/>
-    <mergeCell ref="A27:A31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/doc/Propuesta_cursoRbase.xlsx
+++ b/doc/Propuesta_cursoRbase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\DAT\SAECEPAL\Recursos\Entrenamiento\2025_CursoRbase\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F78BCBD-3A3C-4A33-BECC-BFFC0AFEC7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B4E3D2-E856-41B4-BC33-B4F12655E308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E0571C12-E740-4320-B6A4-84CBC13E1707}"/>
   </bookViews>
@@ -336,7 +336,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -344,23 +344,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -721,280 +718,280 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="4">
         <v>1</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="6">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="4">
         <v>2</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="6">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="4">
         <v>3</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="6">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="4">
         <v>4</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="6">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="4">
         <v>5</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="4">
         <v>1</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="6">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="4">
         <v>2</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="6">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="4">
         <v>3</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="6">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="4">
         <v>4</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="6">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="4">
         <v>5</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="4">
         <v>1</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="6">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="4">
         <v>2</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="6">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="4">
         <v>3</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="6">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="4">
         <v>4</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="6">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="4">
         <v>5</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="4">
         <v>1</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="4" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="6">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="4">
         <v>2</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="6">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="4">
         <v>3</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="6">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="4">
         <v>4</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="6">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="4">
         <v>5</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="4">
         <v>1</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="6">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="4">
         <v>2</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="6">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="4">
         <v>3</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="4" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="6">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="4">
         <v>4</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="6">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="4">
         <v>5</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="4" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="7" t="s">
         <v>69</v>
       </c>
       <c r="C27" s="1">
@@ -1005,8 +1002,8 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
       <c r="C28" s="1">
         <v>2</v>
       </c>
@@ -1015,8 +1012,8 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
       <c r="C29" s="1">
         <v>3</v>
       </c>
@@ -1025,8 +1022,8 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
       <c r="C30" s="1">
         <v>4</v>
       </c>
@@ -1035,8 +1032,8 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
       <c r="C31" s="1">
         <v>5</v>
       </c>
@@ -1045,64 +1042,64 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="4">
         <v>1</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="4" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="1">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="4">
         <v>2</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="1">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="4">
         <v>3</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="1">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="4">
         <v>4</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="1">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="4">
         <v>5</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="5" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C37" s="1">
@@ -1113,8 +1110,8 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
       <c r="C38" s="1">
         <v>2</v>
       </c>
@@ -1123,8 +1120,8 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
       <c r="C39" s="1">
         <v>3</v>
       </c>
@@ -1133,8 +1130,8 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
       <c r="C40" s="1">
         <v>4</v>
       </c>
@@ -1143,8 +1140,8 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
       <c r="C41" s="1">
         <v>5</v>
       </c>
@@ -1153,10 +1150,10 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C42" s="1">
@@ -1167,8 +1164,8 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
+      <c r="A43" s="7"/>
+      <c r="B43" s="7"/>
       <c r="C43" s="1">
         <v>2</v>
       </c>
@@ -1177,8 +1174,8 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
       <c r="C44" s="1">
         <v>3</v>
       </c>
@@ -1187,8 +1184,8 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
       <c r="C45" s="1">
         <v>4</v>
       </c>
@@ -1197,8 +1194,8 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="4"/>
-      <c r="B46" s="4"/>
+      <c r="A46" s="7"/>
+      <c r="B46" s="7"/>
       <c r="C46" s="1">
         <v>5</v>
       </c>
@@ -1207,10 +1204,10 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="7" t="s">
         <v>72</v>
       </c>
       <c r="C47" s="1">
@@ -1221,8 +1218,8 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="4"/>
-      <c r="B48" s="4"/>
+      <c r="A48" s="7"/>
+      <c r="B48" s="7"/>
       <c r="C48" s="1">
         <v>2</v>
       </c>
@@ -1231,8 +1228,8 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="4"/>
-      <c r="B49" s="4"/>
+      <c r="A49" s="7"/>
+      <c r="B49" s="7"/>
       <c r="C49" s="1">
         <v>3</v>
       </c>
@@ -1241,8 +1238,8 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="4"/>
-      <c r="B50" s="4"/>
+      <c r="A50" s="7"/>
+      <c r="B50" s="7"/>
       <c r="C50" s="1">
         <v>4</v>
       </c>
@@ -1251,8 +1248,8 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="4"/>
-      <c r="B51" s="4"/>
+      <c r="A51" s="7"/>
+      <c r="B51" s="7"/>
       <c r="C51" s="1">
         <v>5</v>
       </c>
@@ -1262,26 +1259,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="B27:B31"/>
+    <mergeCell ref="B32:B36"/>
+    <mergeCell ref="B37:B41"/>
+    <mergeCell ref="B42:B46"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="B17:B21"/>
+    <mergeCell ref="B22:B26"/>
     <mergeCell ref="A12:A16"/>
     <mergeCell ref="A17:A21"/>
     <mergeCell ref="A22:A26"/>
     <mergeCell ref="A27:A31"/>
     <mergeCell ref="A47:A51"/>
     <mergeCell ref="A37:A41"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="B7:B11"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="B17:B21"/>
-    <mergeCell ref="B22:B26"/>
-    <mergeCell ref="B27:B31"/>
-    <mergeCell ref="B32:B36"/>
-    <mergeCell ref="B37:B41"/>
-    <mergeCell ref="B42:B46"/>
-    <mergeCell ref="B47:B51"/>
     <mergeCell ref="A32:A36"/>
     <mergeCell ref="A42:A46"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="A7:A11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/doc/Propuesta_cursoRbase.xlsx
+++ b/doc/Propuesta_cursoRbase.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\DAT\SAECEPAL\Recursos\Entrenamiento\2025_CursoRbase\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B4E3D2-E856-41B4-BC33-B4F12655E308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613397CF-B16E-43BE-826C-644B640FC24B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E0571C12-E740-4320-B6A4-84CBC13E1707}"/>
   </bookViews>
@@ -336,7 +336,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -354,9 +354,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -988,56 +985,56 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="4">
         <v>1</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="1">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="4">
         <v>2</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="1">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="4">
         <v>3</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="1">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="4">
         <v>4</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="1">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="4">
         <v>5</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="4" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1096,164 +1093,164 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C37" s="4">
         <v>1</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="7"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="1">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="4">
         <v>2</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="4" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="7"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="1">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="4">
         <v>3</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="4" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="1">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="4">
         <v>4</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="4" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="1">
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="4">
         <v>5</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="4" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C42" s="1">
+      <c r="C42" s="4">
         <v>1</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="1">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="4">
         <v>2</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="1">
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="4">
         <v>3</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="7"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="1">
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="4">
         <v>4</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="7"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="1">
+      <c r="A46" s="6"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="4">
         <v>5</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C47" s="1">
+      <c r="C47" s="4">
         <v>1</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="7"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="1">
+      <c r="A48" s="6"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="4">
         <v>2</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="7"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="1">
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="4">
         <v>3</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="7"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="1">
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="4">
         <v>4</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="4" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="7"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="1">
+      <c r="A51" s="6"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="4">
         <v>5</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="4" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1264,21 +1261,21 @@
     <mergeCell ref="B27:B31"/>
     <mergeCell ref="B32:B36"/>
     <mergeCell ref="B37:B41"/>
-    <mergeCell ref="B42:B46"/>
-    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="A27:A31"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="B7:B11"/>
     <mergeCell ref="B12:B16"/>
     <mergeCell ref="B17:B21"/>
     <mergeCell ref="B22:B26"/>
-    <mergeCell ref="A12:A16"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A26"/>
-    <mergeCell ref="A27:A31"/>
     <mergeCell ref="A47:A51"/>
     <mergeCell ref="A37:A41"/>
     <mergeCell ref="A32:A36"/>
     <mergeCell ref="A42:A46"/>
+    <mergeCell ref="B42:B46"/>
+    <mergeCell ref="B47:B51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/doc/Propuesta_cursoRbase.xlsx
+++ b/doc/Propuesta_cursoRbase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\DAT\SAECEPAL\Recursos\Entrenamiento\2025_CursoRbase\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613397CF-B16E-43BE-826C-644B640FC24B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9AA6F11-A97B-4EE4-BED8-2FDBA4A5C2EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E0571C12-E740-4320-B6A4-84CBC13E1707}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E0571C12-E740-4320-B6A4-84CBC13E1707}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="80">
   <si>
     <t>Clase</t>
   </si>
@@ -269,6 +269,24 @@
   </si>
   <si>
     <t>Lecturas y exportación de bases de datos - librerías - objetos de R</t>
+  </si>
+  <si>
+    <t>Giovanny</t>
+  </si>
+  <si>
+    <t>Jose Fernando</t>
+  </si>
+  <si>
+    <t>Stalyn</t>
+  </si>
+  <si>
+    <t>Encargada/o video clip</t>
+  </si>
+  <si>
+    <t>Vanessa</t>
+  </si>
+  <si>
+    <t>Andres</t>
   </si>
 </sst>
 </file>
@@ -298,7 +316,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -332,11 +350,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -352,6 +379,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -690,17 +723,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A52B075E-DA0A-4FC8-90FD-7548AB994679}">
-  <dimension ref="A1:D51"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E51"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" style="2"/>
-    <col min="4" max="4" width="60.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="2"/>
+    <col min="1" max="1" width="14.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.26953125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" style="2"/>
+    <col min="4" max="4" width="60.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.26953125" style="6" customWidth="1"/>
+    <col min="6" max="16384" width="8.81640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>61</v>
       </c>
@@ -713,12 +747,15 @@
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="E1" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>63</v>
       </c>
       <c r="C2" s="4">
@@ -727,52 +764,59 @@
       <c r="D2" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
+      <c r="E2" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="4">
         <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="4">
         <v>3</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
       <c r="C5" s="4">
         <v>4</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="4">
         <v>5</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="8" t="s">
         <v>64</v>
       </c>
       <c r="C7" s="4">
@@ -781,52 +825,59 @@
       <c r="D7" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
+      <c r="E7" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
       <c r="C8" s="4">
         <v>2</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="4">
         <v>3</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="4">
         <v>4</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
       <c r="C11" s="4">
         <v>5</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="8" t="s">
         <v>65</v>
       </c>
       <c r="C12" s="4">
@@ -835,52 +886,59 @@
       <c r="D12" s="4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
+      <c r="E12" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="4">
         <v>2</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
       <c r="C14" s="4">
         <v>3</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
       <c r="C15" s="4">
         <v>4</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
       <c r="C16" s="4">
         <v>5</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="E16" s="7"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="8" t="s">
         <v>66</v>
       </c>
       <c r="C17" s="4">
@@ -889,52 +947,59 @@
       <c r="D17" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
+      <c r="E17" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
       <c r="C18" s="4">
         <v>2</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
+      <c r="E18" s="7"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
       <c r="C19" s="4">
         <v>3</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
+      <c r="E19" s="7"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
       <c r="C20" s="4">
         <v>4</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
       <c r="C21" s="4">
         <v>5</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="8" t="s">
         <v>67</v>
       </c>
       <c r="C22" s="4">
@@ -943,52 +1008,59 @@
       <c r="D22" s="4" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
+      <c r="E22" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
       <c r="C23" s="4">
         <v>2</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
+      <c r="E23" s="7"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
       <c r="C24" s="4">
         <v>3</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
+      <c r="E24" s="7"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
       <c r="C25" s="4">
         <v>4</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
       <c r="C26" s="4">
         <v>5</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="8" t="s">
         <v>69</v>
       </c>
       <c r="C27" s="4">
@@ -997,52 +1069,59 @@
       <c r="D27" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
+      <c r="E27" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
       <c r="C28" s="4">
         <v>2</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
       <c r="C29" s="4">
         <v>3</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
+      <c r="E29" s="7"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
       <c r="C30" s="4">
         <v>4</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
       <c r="C31" s="4">
         <v>5</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="8" t="s">
         <v>70</v>
       </c>
       <c r="C32" s="4">
@@ -1051,52 +1130,59 @@
       <c r="D32" s="4" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
+      <c r="E32" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
       <c r="C33" s="4">
         <v>2</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
+      <c r="E33" s="7"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
       <c r="C34" s="4">
         <v>3</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
+      <c r="E34" s="7"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
       <c r="C35" s="4">
         <v>4</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
+      <c r="E35" s="7"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
       <c r="C36" s="4">
         <v>5</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
+      <c r="E36" s="7"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="8" t="s">
         <v>68</v>
       </c>
       <c r="C37" s="4">
@@ -1105,52 +1191,59 @@
       <c r="D37" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
+      <c r="E37" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" s="8"/>
+      <c r="B38" s="8"/>
       <c r="C38" s="4">
         <v>2</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
+      <c r="E38" s="7"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" s="8"/>
+      <c r="B39" s="8"/>
       <c r="C39" s="4">
         <v>3</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
+      <c r="E39" s="7"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
       <c r="C40" s="4">
         <v>4</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
+      <c r="E40" s="7"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" s="8"/>
+      <c r="B41" s="8"/>
       <c r="C41" s="4">
         <v>5</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
+      <c r="E41" s="7"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="8" t="s">
         <v>71</v>
       </c>
       <c r="C42" s="4">
@@ -1159,52 +1252,59 @@
       <c r="D42" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
+      <c r="E42" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" s="8"/>
+      <c r="B43" s="8"/>
       <c r="C43" s="4">
         <v>2</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="6"/>
-      <c r="B44" s="6"/>
+      <c r="E43" s="7"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" s="8"/>
+      <c r="B44" s="8"/>
       <c r="C44" s="4">
         <v>3</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
+      <c r="E44" s="7"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" s="8"/>
+      <c r="B45" s="8"/>
       <c r="C45" s="4">
         <v>4</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="6"/>
-      <c r="B46" s="6"/>
+      <c r="E45" s="7"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" s="8"/>
+      <c r="B46" s="8"/>
       <c r="C46" s="4">
         <v>5</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
+      <c r="E46" s="7"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C47" s="4">
@@ -1213,49 +1313,56 @@
       <c r="D47" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6"/>
+      <c r="E47" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
       <c r="C48" s="4">
         <v>2</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6"/>
+      <c r="E48" s="7"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" s="8"/>
+      <c r="B49" s="8"/>
       <c r="C49" s="4">
         <v>3</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
+      <c r="E49" s="7"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" s="8"/>
+      <c r="B50" s="8"/>
       <c r="C50" s="4">
         <v>4</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="6"/>
-      <c r="B51" s="6"/>
+      <c r="E50" s="7"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" s="8"/>
+      <c r="B51" s="8"/>
       <c r="C51" s="4">
         <v>5</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>60</v>
       </c>
+      <c r="E51" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="30">
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="A7:A11"/>
     <mergeCell ref="B27:B31"/>
@@ -1276,6 +1383,16 @@
     <mergeCell ref="A42:A46"/>
     <mergeCell ref="B42:B46"/>
     <mergeCell ref="B47:B51"/>
+    <mergeCell ref="E47:E51"/>
+    <mergeCell ref="E32:E36"/>
+    <mergeCell ref="E37:E41"/>
+    <mergeCell ref="E42:E46"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="E22:E26"/>
+    <mergeCell ref="E27:E31"/>
+    <mergeCell ref="E17:E21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
